--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD3F280-EE53-4DD8-96D0-A7E9B99A1E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC79028D-2D58-44B3-93D7-5BA77ABAD64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -317,6 +317,15 @@
   </si>
   <si>
     <t xml:space="preserve">learning code and improving typing speed </t>
+  </si>
+  <si>
+    <t>aptiti</t>
+  </si>
+  <si>
+    <t>studied c++ and aptitude  test</t>
+  </si>
+  <si>
+    <t>aptitide  test learning ,and slept for 3 hrs because I am not feeling well.</t>
   </si>
 </sst>
 </file>
@@ -2474,7 +2483,7 @@
         <v>51</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2523,27 +2532,51 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+    <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B37" s="14">
+        <v>500</v>
+      </c>
+      <c r="C37" s="14">
+        <v>40</v>
+      </c>
+      <c r="D37" s="14">
+        <v>240</v>
+      </c>
+      <c r="E37" s="14">
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <v>0</v>
+      </c>
+      <c r="G37" s="14">
+        <v>0</v>
+      </c>
+      <c r="H37" s="14">
+        <v>500</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC79028D-2D58-44B3-93D7-5BA77ABAD64B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EB8AE2-C070-410F-8D98-5934F6199AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,19 +313,16 @@
     <t xml:space="preserve">not able to concentrate , watched movie </t>
   </si>
   <si>
-    <t>studied c++ and appitute  test</t>
-  </si>
-  <si>
     <t xml:space="preserve">learning code and improving typing speed </t>
-  </si>
-  <si>
-    <t>aptiti</t>
   </si>
   <si>
     <t>studied c++ and aptitude  test</t>
   </si>
   <si>
     <t>aptitide  test learning ,and slept for 3 hrs because I am not feeling well.</t>
+  </si>
+  <si>
+    <t>got the feedback in english class and tryinh to inprove that and gaveb the test and reading book</t>
   </si>
 </sst>
 </file>
@@ -2483,7 +2480,7 @@
         <v>51</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2529,7 +2526,7 @@
         <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2575,30 +2572,54 @@
         <v>65</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B38" s="14">
+        <v>450</v>
+      </c>
+      <c r="C38" s="14">
+        <v>50</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>120</v>
+      </c>
+      <c r="F38" s="14">
+        <v>200</v>
+      </c>
+      <c r="G38" s="14">
+        <v>4</v>
+      </c>
+      <c r="H38" s="14">
+        <v>450</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EB8AE2-C070-410F-8D98-5934F6199AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A205B949-FFF8-42DC-8B2A-A4A9A072E2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -322,7 +322,10 @@
     <t>aptitide  test learning ,and slept for 3 hrs because I am not feeling well.</t>
   </si>
   <si>
-    <t>got the feedback in english class and tryinh to inprove that and gaveb the test and reading book</t>
+    <t>got the feedback in english class and tryinh to improve that and gave  the test and reading book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not feeling well today , and feeling sleepy </t>
   </si>
 </sst>
 </file>
@@ -2621,27 +2624,51 @@
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+    <row r="39" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A39" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="14">
+        <v>450</v>
+      </c>
+      <c r="C39" s="14">
+        <v>50</v>
+      </c>
+      <c r="D39" s="14">
+        <v>90</v>
+      </c>
+      <c r="E39" s="14">
+        <v>120</v>
+      </c>
+      <c r="F39" s="14">
+        <v>250</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14">
+        <v>420</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A205B949-FFF8-42DC-8B2A-A4A9A072E2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AE8DC8-D2F4-46A9-8C7F-FB2FCDE83E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -326,6 +326,9 @@
   </si>
   <si>
     <t xml:space="preserve">not feeling well today , and feeling sleepy </t>
+  </si>
+  <si>
+    <t xml:space="preserve">practicing maths </t>
   </si>
 </sst>
 </file>
@@ -2671,26 +2674,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B40" s="14">
+        <v>500</v>
+      </c>
+      <c r="C40" s="14">
+        <v>50</v>
+      </c>
+      <c r="D40" s="14">
+        <v>240</v>
+      </c>
+      <c r="E40" s="14">
+        <v>0</v>
+      </c>
+      <c r="F40" s="14">
+        <v>100</v>
+      </c>
+      <c r="G40" s="14">
+        <v>2</v>
+      </c>
+      <c r="H40" s="14">
+        <v>420</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>130</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AE8DC8-D2F4-46A9-8C7F-FB2FCDE83E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B06586B-93A3-448A-9699-F4F888D98635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -329,6 +329,9 @@
   </si>
   <si>
     <t xml:space="preserve">practicing maths </t>
+  </si>
+  <si>
+    <t xml:space="preserve">stydying for CA and because of that I did'nt able to manage time for self study </t>
   </si>
 </sst>
 </file>
@@ -2719,27 +2722,51 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+    <row r="41" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B41" s="14">
+        <v>450</v>
+      </c>
+      <c r="C41" s="14">
+        <v>50</v>
+      </c>
+      <c r="D41" s="14">
+        <v>240</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>300</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>360</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>40</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B06586B-93A3-448A-9699-F4F888D98635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF30E63A-34E6-49BF-A5A3-0DFAC8605C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t xml:space="preserve">stydying for CA and because of that I did'nt able to manage time for self study </t>
+  </si>
+  <si>
+    <t xml:space="preserve">reas thye news and read for the ca </t>
   </si>
 </sst>
 </file>
@@ -2768,27 +2771,51 @@
         <v>97</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B42" s="14">
+        <v>450</v>
+      </c>
+      <c r="C42" s="14">
+        <v>40</v>
+      </c>
+      <c r="D42" s="14">
+        <v>240</v>
+      </c>
+      <c r="E42" s="14">
+        <v>120</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>180</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF30E63A-34E6-49BF-A5A3-0DFAC8605C6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E69696-E4E1-44A8-A2C2-65C906A4E367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -334,7 +334,10 @@
     <t xml:space="preserve">stydying for CA and because of that I did'nt able to manage time for self study </t>
   </si>
   <si>
-    <t xml:space="preserve">reas thye news and read for the ca </t>
+    <t xml:space="preserve">read the news and read for the ca </t>
+  </si>
+  <si>
+    <t xml:space="preserve">working on the project </t>
   </si>
 </sst>
 </file>
@@ -2818,26 +2821,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B43" s="14">
+        <v>450</v>
+      </c>
+      <c r="C43" s="14">
+        <v>50</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>0</v>
+      </c>
+      <c r="F43" s="14">
+        <v>60</v>
+      </c>
+      <c r="G43" s="14">
+        <v>1</v>
+      </c>
+      <c r="H43" s="14">
+        <v>540</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>160</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E69696-E4E1-44A8-A2C2-65C906A4E367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1F834E-FDA9-4B6E-83B3-946A7CA22B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -338,6 +338,9 @@
   </si>
   <si>
     <t xml:space="preserve">working on the project </t>
+  </si>
+  <si>
+    <t>learning c++ and not able to focus on study today , today day was so stressful and feeling low</t>
   </si>
 </sst>
 </file>
@@ -2866,27 +2869,51 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+    <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B44" s="14">
+        <v>450</v>
+      </c>
+      <c r="C44" s="14">
+        <v>50</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>120</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>360</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1F834E-FDA9-4B6E-83B3-946A7CA22B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21173A8-6082-4A30-8F21-A5B87DA53DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,7 +340,10 @@
     <t xml:space="preserve">working on the project </t>
   </si>
   <si>
-    <t>learning c++ and not able to focus on study today , today day was so stressful and feeling low</t>
+    <t>learning c++ and not able to focus on study today , todays day was so stressful and feeling low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">working on project and learning sql </t>
   </si>
 </sst>
 </file>
@@ -2869,7 +2872,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="13">
         <v>46285</v>
       </c>
@@ -2915,27 +2918,51 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+    <row r="45" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A45" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B45" s="14">
+        <v>480</v>
+      </c>
+      <c r="C45" s="14">
+        <v>50</v>
+      </c>
+      <c r="D45" s="14">
+        <v>90</v>
+      </c>
+      <c r="E45" s="14">
+        <v>180</v>
+      </c>
+      <c r="F45" s="14">
+        <v>200</v>
+      </c>
+      <c r="G45" s="14">
+        <v>4</v>
+      </c>
+      <c r="H45" s="14">
+        <v>360</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>80</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/12609979.xlsx
+++ b/12609979.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python\minorproject1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21173A8-6082-4A30-8F21-A5B87DA53DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9D3EA65-41F3-452D-A60B-BFDEBDCC5620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -344,6 +344,9 @@
   </si>
   <si>
     <t xml:space="preserve">working on project and learning sql </t>
+  </si>
+  <si>
+    <t xml:space="preserve">studying for ca  and working on project </t>
   </si>
 </sst>
 </file>
@@ -2964,27 +2967,51 @@
         <v>101</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+    <row r="46" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A46" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B46" s="14">
+        <v>480</v>
+      </c>
+      <c r="C46" s="14">
+        <v>50</v>
+      </c>
+      <c r="D46" s="14">
+        <v>120</v>
+      </c>
+      <c r="E46" s="14">
+        <v>120</v>
+      </c>
+      <c r="F46" s="14">
+        <v>250</v>
+      </c>
+      <c r="G46" s="14">
+        <v>5</v>
+      </c>
+      <c r="H46" s="14">
+        <v>360</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>
